--- a/data/input/input_case.xlsx
+++ b/data/input/input_case.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\김진중\수업\5-1\작업용 폴더\tunnel-method-recommender\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE434CCE-5264-47CE-8EEE-85997F7431E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD52993E-A11C-400F-8DEE-7789FDD204A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11472" yWindow="792" windowWidth="11520" windowHeight="10956" xr2:uid="{62748EBE-0567-438F-9666-097F55E0F40C}"/>
+    <workbookView xWindow="1536" yWindow="1284" windowWidth="11520" windowHeight="10956" xr2:uid="{62748EBE-0567-438F-9666-097F55E0F40C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -60,22 +60,22 @@
     <t>터널 길이(km)_정규화</t>
   </si>
   <si>
-    <t>고지압</t>
+    <t>매우높음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>침하·변형관리</t>
+  </si>
+  <si>
+    <t>지하수제어</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>암반</t>
+    <t>연약지반</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>낮음</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>수중</t>
+    <t>도심지</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -83,7 +83,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -127,14 +127,6 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -167,7 +159,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -182,9 +174,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -539,28 +528,28 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2" s="4">
-        <v>2000</v>
+        <v>25</v>
       </c>
       <c r="B2" s="4">
-        <v>6.5</v>
+        <v>6.17</v>
       </c>
       <c r="C2" s="4">
-        <v>3.2</v>
+        <v>13</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>12</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="5" t="s">
-        <v>8</v>
+      <c r="H2" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>

--- a/data/input/input_case.xlsx
+++ b/data/input/input_case.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\김진중\수업\5-1\작업용 폴더\tunnel-method-recommender\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD52993E-A11C-400F-8DEE-7789FDD204A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B68541F-FE56-4F17-B475-6AAA02CE4C98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1536" yWindow="1284" windowWidth="11520" windowHeight="10956" xr2:uid="{62748EBE-0567-438F-9666-097F55E0F40C}"/>
+    <workbookView xWindow="11868" yWindow="1632" windowWidth="11520" windowHeight="10956" xr2:uid="{62748EBE-0567-438F-9666-097F55E0F40C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -60,22 +60,22 @@
     <t>터널 길이(km)_정규화</t>
   </si>
   <si>
+    <t>침하·변형관리</t>
+  </si>
+  <si>
+    <t>혼합지반</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>매우높음</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>침하·변형관리</t>
-  </si>
-  <si>
-    <t>지하수제어</t>
+    <t>수밀성확보</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>연약지반</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>도심지</t>
+    <t>도시복합</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -528,28 +528,28 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="B2" s="4">
-        <v>6.17</v>
+        <v>11</v>
       </c>
       <c r="C2" s="4">
-        <v>13</v>
+        <v>5.8</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>12</v>
       </c>
       <c r="F2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" t="s">
         <v>8</v>
       </c>
-      <c r="G2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>10</v>
+      <c r="H2" t="s">
+        <v>11</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>

--- a/data/input/input_case.xlsx
+++ b/data/input/input_case.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\김진중\수업\5-1\작업용 폴더\tunnel-method-recommender\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B68541F-FE56-4F17-B475-6AAA02CE4C98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B55AFF5-3011-4DEC-9830-46B5C35D8299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11868" yWindow="1632" windowWidth="11520" windowHeight="10956" xr2:uid="{62748EBE-0567-438F-9666-097F55E0F40C}"/>
+    <workbookView xWindow="11520" yWindow="1284" windowWidth="11520" windowHeight="10956" xr2:uid="{62748EBE-0567-438F-9666-097F55E0F40C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -60,30 +60,29 @@
     <t>터널 길이(km)_정규화</t>
   </si>
   <si>
-    <t>침하·변형관리</t>
+    <t>높음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수압·수밀관리</t>
+  </si>
+  <si>
+    <t>하천 하부</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>혼합지반</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>매우높음</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>수밀성확보</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>도시복합</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>내구성·안정성</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -127,6 +126,13 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -154,12 +160,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -175,9 +182,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="표준 2" xfId="1" xr:uid="{AC1F16D4-2813-4626-8A3C-143F07A8C947}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -528,28 +537,28 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="B2" s="4">
+        <v>7.76</v>
+      </c>
+      <c r="C2" s="4">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="4">
-        <v>5.8</v>
-      </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="H2" s="5" t="s">
         <v>12</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" t="s">
-        <v>11</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>

--- a/data/input/input_case.xlsx
+++ b/data/input/input_case.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\김진중\수업\5-1\작업용 폴더\tunnel-method-recommender\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B55AFF5-3011-4DEC-9830-46B5C35D8299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A1C6F21-31F0-4201-9DAC-89A8F400D5AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11520" yWindow="1284" windowWidth="11520" windowHeight="10956" xr2:uid="{62748EBE-0567-438F-9666-097F55E0F40C}"/>
+    <workbookView xWindow="13248" yWindow="1056" windowWidth="11520" windowHeight="10956" xr2:uid="{62748EBE-0567-438F-9666-097F55E0F40C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -60,29 +60,30 @@
     <t>터널 길이(km)_정규화</t>
   </si>
   <si>
-    <t>높음</t>
+    <t>도심지</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>매우높음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>수압·수밀관리</t>
-  </si>
-  <si>
-    <t>하천 하부</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>혼합지반</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>내구성·안정성</t>
+    <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -132,6 +133,19 @@
       <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="2">
@@ -166,7 +180,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -182,7 +196,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -537,27 +554,27 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2" s="4">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B2" s="4">
-        <v>7.76</v>
+        <v>7.9</v>
       </c>
       <c r="C2" s="4">
-        <v>1.1000000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="6" t="s">
         <v>12</v>
       </c>
       <c r="I2" s="1"/>

--- a/data/input/input_case.xlsx
+++ b/data/input/input_case.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\김진중\수업\5-1\작업용 폴더\tunnel-method-recommender\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A1C6F21-31F0-4201-9DAC-89A8F400D5AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{430F3346-318D-4882-A676-6806DC3CC945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13248" yWindow="1056" windowWidth="11520" windowHeight="10956" xr2:uid="{62748EBE-0567-438F-9666-097F55E0F40C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{62748EBE-0567-438F-9666-097F55E0F40C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -60,30 +60,26 @@
     <t>터널 길이(km)_정규화</t>
   </si>
   <si>
+    <t>암반</t>
+  </si>
+  <si>
     <t>도심지</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>매우높음</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>수압·수밀관리</t>
-  </si>
-  <si>
-    <t>혼합지반</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지하수위제어</t>
   </si>
   <si>
     <t>-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -124,25 +120,11 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
@@ -178,9 +160,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -193,12 +175,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -553,28 +531,28 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A2" s="4">
-        <v>15</v>
-      </c>
-      <c r="B2" s="4">
-        <v>7.9</v>
-      </c>
-      <c r="C2" s="4">
-        <v>1.2</v>
-      </c>
-      <c r="D2" s="4" t="s">
+      <c r="A2">
+        <v>25</v>
+      </c>
+      <c r="B2">
+        <v>9.5</v>
+      </c>
+      <c r="C2">
+        <v>3.1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" t="s">
         <v>12</v>
       </c>
       <c r="I2" s="1"/>
@@ -593,27 +571,19 @@
       <c r="J3" s="1"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
       <c r="J5" s="1"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.4">
